--- a/TABELA FOB AGOSTO 2026 xlsx.xlsx
+++ b/TABELA FOB AGOSTO 2026 xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f9d5c715c185684/Área de Trabalho/Automação Dados/Automação Distribuição/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF1510C-32BC-47FF-8562-D989EF59D420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{8EF1510C-32BC-47FF-8562-D989EF59D420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{763C4F60-57D9-42CD-9B8C-A834E1B0C234}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="9255" yWindow="5730" windowWidth="16470" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FOB" sheetId="1" r:id="rId1"/>
@@ -11055,6 +11055,120 @@
     <xf numFmtId="49" fontId="9" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="28" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="42" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="42" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="42" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -11102,120 +11216,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="28" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="42" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="42" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="42" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11700,48 +11700,48 @@
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" style="39" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
     <col min="10" max="10" width="21.42578125" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="49" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" style="49" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" style="49" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="49" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="28" hidden="1" customWidth="1"/>
-    <col min="16" max="17" width="14.5703125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="21" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="17.42578125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="19" hidden="1" customWidth="1"/>
-    <col min="21" max="22" width="16.7109375" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="24" max="25" width="16.7109375" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="20.7109375" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="23.5703125" hidden="1" customWidth="1"/>
-    <col min="28" max="29" width="22.7109375" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="21.85546875" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="8.85546875" style="28" hidden="1" customWidth="1"/>
-    <col min="32" max="34" width="0" style="28" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="49" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" style="49" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" style="49" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="49" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="28" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" customWidth="1"/>
+    <col min="18" max="18" width="21" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" customWidth="1"/>
+    <col min="20" max="20" width="19" customWidth="1"/>
+    <col min="21" max="22" width="16.7109375" customWidth="1"/>
+    <col min="23" max="23" width="25.7109375" customWidth="1"/>
+    <col min="24" max="25" width="16.7109375" customWidth="1"/>
+    <col min="26" max="26" width="20.7109375" customWidth="1"/>
+    <col min="27" max="27" width="23.5703125" customWidth="1"/>
+    <col min="28" max="29" width="22.7109375" customWidth="1"/>
+    <col min="30" max="30" width="21.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.85546875" style="28" customWidth="1"/>
+    <col min="32" max="34" width="9.140625" style="28" customWidth="1"/>
     <col min="35" max="395" width="9.140625" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="135"/>
-      <c r="B1" s="464" t="s">
+      <c r="B1" s="433" t="s">
         <v>1011</v>
       </c>
-      <c r="C1" s="464"/>
-      <c r="D1" s="465" t="s">
+      <c r="C1" s="433"/>
+      <c r="D1" s="434" t="s">
         <v>569</v>
       </c>
-      <c r="E1" s="466"/>
-      <c r="F1" s="467" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="468"/>
-      <c r="H1" s="469">
+      <c r="E1" s="435"/>
+      <c r="F1" s="436" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="437"/>
+      <c r="H1" s="438">
         <v>46235</v>
       </c>
-      <c r="I1" s="470"/>
-      <c r="J1" s="471"/>
+      <c r="I1" s="439"/>
+      <c r="J1" s="440"/>
       <c r="K1" s="139"/>
       <c r="L1" s="139"/>
       <c r="M1" s="139"/>
@@ -11769,19 +11769,19 @@
     </row>
     <row r="2" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="135"/>
-      <c r="B2" s="472" t="s">
+      <c r="B2" s="430" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="472"/>
+      <c r="C2" s="430"/>
       <c r="D2" s="142"/>
       <c r="E2" s="254" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="474"/>
-      <c r="G2" s="474"/>
-      <c r="H2" s="474"/>
-      <c r="I2" s="474"/>
-      <c r="J2" s="474"/>
+      <c r="F2" s="441"/>
+      <c r="G2" s="441"/>
+      <c r="H2" s="441"/>
+      <c r="I2" s="441"/>
+      <c r="J2" s="441"/>
       <c r="K2" s="139"/>
       <c r="L2" s="139"/>
       <c r="M2" s="139"/>
@@ -11809,19 +11809,19 @@
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="135"/>
-      <c r="B3" s="472" t="s">
+      <c r="B3" s="430" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="472"/>
+      <c r="C3" s="430"/>
       <c r="D3" s="143"/>
       <c r="E3" s="254" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="473"/>
-      <c r="G3" s="473"/>
-      <c r="H3" s="473"/>
-      <c r="I3" s="473"/>
-      <c r="J3" s="473"/>
+      <c r="F3" s="429"/>
+      <c r="G3" s="429"/>
+      <c r="H3" s="429"/>
+      <c r="I3" s="429"/>
+      <c r="J3" s="429"/>
       <c r="K3" s="139"/>
       <c r="L3" s="139"/>
       <c r="M3" s="139"/>
@@ -11849,19 +11849,19 @@
     </row>
     <row r="4" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="135"/>
-      <c r="B4" s="472" t="s">
+      <c r="B4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="472"/>
+      <c r="C4" s="430"/>
       <c r="D4" s="143"/>
       <c r="E4" s="254" t="s">
         <v>283</v>
       </c>
-      <c r="F4" s="473"/>
-      <c r="G4" s="473"/>
-      <c r="H4" s="473"/>
-      <c r="I4" s="473"/>
-      <c r="J4" s="473"/>
+      <c r="F4" s="429"/>
+      <c r="G4" s="429"/>
+      <c r="H4" s="429"/>
+      <c r="I4" s="429"/>
+      <c r="J4" s="429"/>
       <c r="K4" s="139"/>
       <c r="L4" s="139"/>
       <c r="M4" s="139"/>
@@ -11929,19 +11929,19 @@
     </row>
     <row r="6" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="135"/>
-      <c r="B6" s="472" t="s">
+      <c r="B6" s="430" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="472"/>
+      <c r="C6" s="430"/>
       <c r="D6" s="143"/>
       <c r="E6" s="254" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="473"/>
-      <c r="G6" s="473"/>
-      <c r="H6" s="473"/>
-      <c r="I6" s="473"/>
-      <c r="J6" s="473"/>
+      <c r="F6" s="429"/>
+      <c r="G6" s="429"/>
+      <c r="H6" s="429"/>
+      <c r="I6" s="429"/>
+      <c r="J6" s="429"/>
       <c r="K6" s="139"/>
       <c r="L6" s="139"/>
       <c r="M6" s="139"/>
@@ -11969,19 +11969,19 @@
     </row>
     <row r="7" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="135"/>
-      <c r="B7" s="472" t="s">
+      <c r="B7" s="430" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="472"/>
+      <c r="C7" s="430"/>
       <c r="D7" s="143"/>
       <c r="E7" s="254" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="473"/>
-      <c r="G7" s="473"/>
-      <c r="H7" s="473"/>
-      <c r="I7" s="473"/>
-      <c r="J7" s="473"/>
+      <c r="F7" s="429"/>
+      <c r="G7" s="429"/>
+      <c r="H7" s="429"/>
+      <c r="I7" s="429"/>
+      <c r="J7" s="429"/>
       <c r="K7" s="139"/>
       <c r="L7" s="139"/>
       <c r="M7" s="139"/>
@@ -12009,10 +12009,10 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="135"/>
-      <c r="B8" s="475" t="s">
+      <c r="B8" s="431" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="476"/>
+      <c r="C8" s="432"/>
       <c r="D8" s="145" t="s">
         <v>572</v>
       </c>
@@ -12052,8 +12052,8 @@
       <c r="B9" s="255" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="456"/>
-      <c r="D9" s="457"/>
+      <c r="C9" s="444"/>
+      <c r="D9" s="445"/>
       <c r="E9" s="139"/>
       <c r="F9" s="139"/>
       <c r="G9" s="147"/>
@@ -12127,11 +12127,11 @@
       <c r="C11" s="139"/>
       <c r="D11" s="139"/>
       <c r="E11" s="139"/>
-      <c r="F11" s="458" t="s">
+      <c r="F11" s="446" t="s">
         <v>575</v>
       </c>
-      <c r="G11" s="459"/>
-      <c r="H11" s="460"/>
+      <c r="G11" s="447"/>
+      <c r="H11" s="448"/>
       <c r="I11" s="150"/>
       <c r="J11" s="139"/>
       <c r="K11" s="139"/>
@@ -12168,11 +12168,11 @@
       <c r="F12" s="256" t="s">
         <v>574</v>
       </c>
-      <c r="G12" s="454">
+      <c r="G12" s="442">
         <f>E201</f>
         <v>0</v>
       </c>
-      <c r="H12" s="455"/>
+      <c r="H12" s="443"/>
       <c r="I12" s="152"/>
       <c r="J12" s="139"/>
       <c r="K12" s="139"/>
@@ -12209,11 +12209,11 @@
       <c r="F13" s="256" t="s">
         <v>596</v>
       </c>
-      <c r="G13" s="454">
+      <c r="G13" s="442">
         <f>E203</f>
         <v>0</v>
       </c>
-      <c r="H13" s="455"/>
+      <c r="H13" s="443"/>
       <c r="I13" s="152"/>
       <c r="J13" s="139"/>
       <c r="K13" s="139"/>
@@ -12295,23 +12295,23 @@
       <c r="M15" s="139"/>
       <c r="N15" s="139"/>
       <c r="O15" s="140"/>
-      <c r="P15" s="461" t="s">
+      <c r="P15" s="449" t="s">
         <v>880</v>
       </c>
-      <c r="Q15" s="462"/>
-      <c r="R15" s="462"/>
-      <c r="S15" s="462"/>
-      <c r="T15" s="462"/>
-      <c r="U15" s="462"/>
-      <c r="V15" s="462"/>
-      <c r="W15" s="462"/>
-      <c r="X15" s="462"/>
-      <c r="Y15" s="462"/>
-      <c r="Z15" s="462"/>
-      <c r="AA15" s="462"/>
-      <c r="AB15" s="462"/>
-      <c r="AC15" s="462"/>
-      <c r="AD15" s="463"/>
+      <c r="Q15" s="450"/>
+      <c r="R15" s="450"/>
+      <c r="S15" s="450"/>
+      <c r="T15" s="450"/>
+      <c r="U15" s="450"/>
+      <c r="V15" s="450"/>
+      <c r="W15" s="450"/>
+      <c r="X15" s="450"/>
+      <c r="Y15" s="450"/>
+      <c r="Z15" s="450"/>
+      <c r="AA15" s="450"/>
+      <c r="AB15" s="450"/>
+      <c r="AC15" s="450"/>
+      <c r="AD15" s="451"/>
       <c r="AE15" s="133"/>
       <c r="AF15" s="133"/>
       <c r="AG15" s="133"/>
@@ -47220,16 +47220,16 @@
     </row>
     <row r="197" spans="1:395" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="135"/>
-      <c r="B197" s="442"/>
-      <c r="C197" s="443"/>
+      <c r="B197" s="452"/>
+      <c r="C197" s="453"/>
       <c r="D197" s="222" t="s">
         <v>875</v>
       </c>
-      <c r="E197" s="434" t="e">
+      <c r="E197" s="472" t="e">
         <f>AB195</f>
         <v>#REF!</v>
       </c>
-      <c r="F197" s="435"/>
+      <c r="F197" s="473"/>
       <c r="G197" s="223"/>
       <c r="H197" s="224"/>
       <c r="I197" s="224"/>
@@ -47261,14 +47261,14 @@
     </row>
     <row r="198" spans="1:395" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="135"/>
-      <c r="B198" s="442"/>
-      <c r="C198" s="443"/>
+      <c r="B198" s="452"/>
+      <c r="C198" s="453"/>
       <c r="D198" s="222"/>
-      <c r="E198" s="434" t="e">
+      <c r="E198" s="472" t="e">
         <f>E197*5%</f>
         <v>#REF!</v>
       </c>
-      <c r="F198" s="435"/>
+      <c r="F198" s="473"/>
       <c r="G198" s="225"/>
       <c r="H198" s="226"/>
       <c r="I198" s="227"/>
@@ -47300,16 +47300,16 @@
     </row>
     <row r="199" spans="1:395" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="135"/>
-      <c r="B199" s="442"/>
-      <c r="C199" s="443"/>
+      <c r="B199" s="452"/>
+      <c r="C199" s="453"/>
       <c r="D199" s="222" t="s">
         <v>876</v>
       </c>
-      <c r="E199" s="434" t="e">
+      <c r="E199" s="472" t="e">
         <f>AC195</f>
         <v>#REF!</v>
       </c>
-      <c r="F199" s="435"/>
+      <c r="F199" s="473"/>
       <c r="G199" s="228"/>
       <c r="H199" s="229"/>
       <c r="I199" s="230"/>
@@ -47341,16 +47341,16 @@
     </row>
     <row r="200" spans="1:395" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="135"/>
-      <c r="B200" s="442"/>
-      <c r="C200" s="443"/>
+      <c r="B200" s="452"/>
+      <c r="C200" s="453"/>
       <c r="D200" s="222" t="s">
         <v>852</v>
       </c>
-      <c r="E200" s="436" t="str">
+      <c r="E200" s="474" t="str">
         <f>Z193</f>
         <v>TOTAL PROMO S/ DESC</v>
       </c>
-      <c r="F200" s="437"/>
+      <c r="F200" s="475"/>
       <c r="G200" s="146"/>
       <c r="H200" s="139"/>
       <c r="I200" s="220"/>
@@ -47382,16 +47382,16 @@
     </row>
     <row r="201" spans="1:395" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="135"/>
-      <c r="B201" s="442"/>
-      <c r="C201" s="443"/>
+      <c r="B201" s="452"/>
+      <c r="C201" s="453"/>
       <c r="D201" s="231" t="s">
         <v>868</v>
       </c>
-      <c r="E201" s="426">
+      <c r="E201" s="464">
         <f>J195</f>
         <v>0</v>
       </c>
-      <c r="F201" s="427"/>
+      <c r="F201" s="465"/>
       <c r="G201" s="200"/>
       <c r="H201" s="139"/>
       <c r="I201" s="220"/>
@@ -47423,16 +47423,16 @@
     </row>
     <row r="202" spans="1:395" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="135"/>
-      <c r="B202" s="442"/>
-      <c r="C202" s="443"/>
+      <c r="B202" s="452"/>
+      <c r="C202" s="453"/>
       <c r="D202" s="231" t="s">
         <v>869</v>
       </c>
-      <c r="E202" s="426">
+      <c r="E202" s="464">
         <f>E201*5%</f>
         <v>0</v>
       </c>
-      <c r="F202" s="427"/>
+      <c r="F202" s="465"/>
       <c r="G202" s="200">
         <v>11998.5</v>
       </c>
@@ -47469,16 +47469,16 @@
     </row>
     <row r="203" spans="1:395" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="135"/>
-      <c r="B203" s="442"/>
-      <c r="C203" s="443"/>
+      <c r="B203" s="452"/>
+      <c r="C203" s="453"/>
       <c r="D203" s="231" t="s">
         <v>869</v>
       </c>
-      <c r="E203" s="426">
+      <c r="E203" s="464">
         <f>E201-E202</f>
         <v>0</v>
       </c>
-      <c r="F203" s="427"/>
+      <c r="F203" s="465"/>
       <c r="G203" s="200"/>
       <c r="H203" s="232"/>
       <c r="I203" s="139"/>
@@ -47512,15 +47512,15 @@
     </row>
     <row r="204" spans="1:395" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="135"/>
-      <c r="B204" s="442"/>
-      <c r="C204" s="443"/>
+      <c r="B204" s="452"/>
+      <c r="C204" s="453"/>
       <c r="D204" s="233" t="s">
         <v>175</v>
       </c>
-      <c r="E204" s="438" t="s">
+      <c r="E204" s="476" t="s">
         <v>176</v>
       </c>
-      <c r="F204" s="439"/>
+      <c r="F204" s="477"/>
       <c r="G204" s="146"/>
       <c r="H204" s="139"/>
       <c r="I204" s="139"/>
@@ -47552,16 +47552,16 @@
     </row>
     <row r="205" spans="1:395" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="135"/>
-      <c r="B205" s="444"/>
-      <c r="C205" s="451"/>
+      <c r="B205" s="454"/>
+      <c r="C205" s="461"/>
       <c r="D205" s="234" t="s">
         <v>177</v>
       </c>
-      <c r="E205" s="440">
+      <c r="E205" s="478">
         <f>SUM(E15:E192)</f>
         <v>0</v>
       </c>
-      <c r="F205" s="441"/>
+      <c r="F205" s="479"/>
       <c r="G205" s="146"/>
       <c r="H205" s="139"/>
       <c r="I205" s="139"/>
@@ -47593,14 +47593,14 @@
     </row>
     <row r="206" spans="1:395" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="135"/>
-      <c r="B206" s="452" t="s">
+      <c r="B206" s="462" t="s">
         <v>178</v>
       </c>
-      <c r="C206" s="453"/>
-      <c r="D206" s="432" t="s">
+      <c r="C206" s="463"/>
+      <c r="D206" s="470" t="s">
         <v>179</v>
       </c>
-      <c r="E206" s="433"/>
+      <c r="E206" s="471"/>
       <c r="F206" s="139"/>
       <c r="G206" s="146"/>
       <c r="H206" s="139"/>
@@ -47669,17 +47669,17 @@
     </row>
     <row r="208" spans="1:395" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="135"/>
-      <c r="B208" s="448" t="s">
+      <c r="B208" s="458" t="s">
         <v>180</v>
       </c>
-      <c r="C208" s="449"/>
+      <c r="C208" s="459"/>
       <c r="D208" s="235" t="s">
         <v>181</v>
       </c>
-      <c r="E208" s="428" t="s">
+      <c r="E208" s="466" t="s">
         <v>887</v>
       </c>
-      <c r="F208" s="429"/>
+      <c r="F208" s="467"/>
       <c r="G208" s="236"/>
       <c r="H208" s="139"/>
       <c r="I208" s="139"/>
@@ -47711,15 +47711,15 @@
     </row>
     <row r="209" spans="1:34" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="135"/>
-      <c r="B209" s="442"/>
-      <c r="C209" s="450"/>
+      <c r="B209" s="452"/>
+      <c r="C209" s="460"/>
       <c r="D209" s="235" t="s">
         <v>571</v>
       </c>
-      <c r="E209" s="430" t="s">
+      <c r="E209" s="468" t="s">
         <v>286</v>
       </c>
-      <c r="F209" s="431"/>
+      <c r="F209" s="469"/>
       <c r="G209" s="237"/>
       <c r="H209" s="238"/>
       <c r="I209" s="238"/>
@@ -47751,8 +47751,8 @@
     </row>
     <row r="210" spans="1:34" ht="22.15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="135"/>
-      <c r="B210" s="444"/>
-      <c r="C210" s="445"/>
+      <c r="B210" s="454"/>
+      <c r="C210" s="455"/>
       <c r="D210" s="235"/>
       <c r="E210" s="139"/>
       <c r="F210" s="238"/>
@@ -47825,10 +47825,10 @@
     </row>
     <row r="212" spans="1:34" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="135"/>
-      <c r="B212" s="446" t="s">
+      <c r="B212" s="456" t="s">
         <v>281</v>
       </c>
-      <c r="C212" s="447"/>
+      <c r="C212" s="457"/>
       <c r="D212" s="242" t="s">
         <v>321</v>
       </c>
@@ -47863,10 +47863,10 @@
     </row>
     <row r="213" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="135"/>
-      <c r="B213" s="442" t="s">
+      <c r="B213" s="452" t="s">
         <v>182</v>
       </c>
-      <c r="C213" s="443"/>
+      <c r="C213" s="453"/>
       <c r="D213" s="243" t="s">
         <v>278</v>
       </c>
@@ -47901,8 +47901,8 @@
     </row>
     <row r="214" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="135"/>
-      <c r="B214" s="442"/>
-      <c r="C214" s="443"/>
+      <c r="B214" s="452"/>
+      <c r="C214" s="453"/>
       <c r="D214" s="244" t="s">
         <v>183</v>
       </c>
@@ -47937,8 +47937,8 @@
     </row>
     <row r="215" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="135"/>
-      <c r="B215" s="442"/>
-      <c r="C215" s="443"/>
+      <c r="B215" s="452"/>
+      <c r="C215" s="453"/>
       <c r="D215" s="244" t="s">
         <v>184</v>
       </c>
@@ -47973,8 +47973,8 @@
     </row>
     <row r="216" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="135"/>
-      <c r="B216" s="442"/>
-      <c r="C216" s="443"/>
+      <c r="B216" s="452"/>
+      <c r="C216" s="453"/>
       <c r="D216" s="244" t="s">
         <v>185</v>
       </c>
@@ -48009,8 +48009,8 @@
     </row>
     <row r="217" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="135"/>
-      <c r="B217" s="442"/>
-      <c r="C217" s="443"/>
+      <c r="B217" s="452"/>
+      <c r="C217" s="453"/>
       <c r="D217" s="244" t="s">
         <v>186</v>
       </c>
@@ -48045,8 +48045,8 @@
     </row>
     <row r="218" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="135"/>
-      <c r="B218" s="442"/>
-      <c r="C218" s="443"/>
+      <c r="B218" s="452"/>
+      <c r="C218" s="453"/>
       <c r="D218" s="244" t="s">
         <v>187</v>
       </c>
@@ -48081,8 +48081,8 @@
     </row>
     <row r="219" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="135"/>
-      <c r="B219" s="442"/>
-      <c r="C219" s="443"/>
+      <c r="B219" s="452"/>
+      <c r="C219" s="453"/>
       <c r="D219" s="244" t="s">
         <v>279</v>
       </c>
@@ -48117,8 +48117,8 @@
     </row>
     <row r="220" spans="1:34" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="135"/>
-      <c r="B220" s="442"/>
-      <c r="C220" s="443"/>
+      <c r="B220" s="452"/>
+      <c r="C220" s="453"/>
       <c r="D220" s="244" t="s">
         <v>188</v>
       </c>
@@ -48153,8 +48153,8 @@
     </row>
     <row r="221" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="135"/>
-      <c r="B221" s="442"/>
-      <c r="C221" s="443"/>
+      <c r="B221" s="452"/>
+      <c r="C221" s="453"/>
       <c r="D221" s="245" t="s">
         <v>188</v>
       </c>
@@ -48189,8 +48189,8 @@
     </row>
     <row r="222" spans="1:34" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="135"/>
-      <c r="B222" s="444"/>
-      <c r="C222" s="445"/>
+      <c r="B222" s="454"/>
+      <c r="C222" s="455"/>
       <c r="D222" s="245" t="s">
         <v>285</v>
       </c>
@@ -53041,31 +53041,6 @@
     <filterColumn colId="27" showButton="0"/>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="P15:AD15"/>
-    <mergeCell ref="B213:C222"/>
-    <mergeCell ref="B212:C212"/>
-    <mergeCell ref="B208:C210"/>
-    <mergeCell ref="B197:C205"/>
-    <mergeCell ref="B206:C206"/>
     <mergeCell ref="E203:F203"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="E209:F209"/>
@@ -53078,6 +53053,31 @@
     <mergeCell ref="E201:F201"/>
     <mergeCell ref="E202:F202"/>
     <mergeCell ref="E198:F198"/>
+    <mergeCell ref="B213:C222"/>
+    <mergeCell ref="B212:C212"/>
+    <mergeCell ref="B208:C210"/>
+    <mergeCell ref="B197:C205"/>
+    <mergeCell ref="B206:C206"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="P15:AD15"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <conditionalFormatting sqref="E200:F200">
@@ -58762,7 +58762,7 @@
       <c r="A199" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="B199" s="478"/>
+      <c r="B199" s="427"/>
       <c r="C199" s="31" t="s">
         <v>321</v>
       </c>
@@ -58773,10 +58773,10 @@
       </c>
     </row>
     <row r="200" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="477" t="s">
+      <c r="A200" s="426" t="s">
         <v>182</v>
       </c>
-      <c r="B200" s="478"/>
+      <c r="B200" s="427"/>
       <c r="C200" s="31" t="s">
         <v>278</v>
       </c>
@@ -58787,8 +58787,8 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="477"/>
-      <c r="B201" s="478"/>
+      <c r="A201" s="426"/>
+      <c r="B201" s="427"/>
       <c r="C201" s="31" t="s">
         <v>1014</v>
       </c>
@@ -58799,8 +58799,8 @@
       </c>
     </row>
     <row r="202" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="477"/>
-      <c r="B202" s="478"/>
+      <c r="A202" s="426"/>
+      <c r="B202" s="427"/>
       <c r="C202" s="32" t="s">
         <v>183</v>
       </c>
@@ -58811,8 +58811,8 @@
       </c>
     </row>
     <row r="203" spans="1:8" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="477"/>
-      <c r="B203" s="478"/>
+      <c r="A203" s="426"/>
+      <c r="B203" s="427"/>
       <c r="C203" s="32" t="s">
         <v>184</v>
       </c>
@@ -58823,8 +58823,8 @@
       </c>
     </row>
     <row r="204" spans="1:8" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="477"/>
-      <c r="B204" s="478"/>
+      <c r="A204" s="426"/>
+      <c r="B204" s="427"/>
       <c r="C204" s="32" t="s">
         <v>185</v>
       </c>
@@ -58835,8 +58835,8 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="477"/>
-      <c r="B205" s="478"/>
+      <c r="A205" s="426"/>
+      <c r="B205" s="427"/>
       <c r="C205" s="32" t="s">
         <v>186</v>
       </c>
@@ -58847,8 +58847,8 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="477"/>
-      <c r="B206" s="478"/>
+      <c r="A206" s="426"/>
+      <c r="B206" s="427"/>
       <c r="C206" s="32" t="s">
         <v>187</v>
       </c>
@@ -58859,8 +58859,8 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="477"/>
-      <c r="B207" s="478"/>
+      <c r="A207" s="426"/>
+      <c r="B207" s="427"/>
       <c r="C207" s="32" t="s">
         <v>279</v>
       </c>
@@ -58872,7 +58872,7 @@
     </row>
     <row r="208" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="71"/>
-      <c r="B208" s="478"/>
+      <c r="B208" s="427"/>
       <c r="C208" s="32" t="s">
         <v>188</v>
       </c>
@@ -58884,7 +58884,7 @@
     </row>
     <row r="209" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="114"/>
-      <c r="B209" s="479"/>
+      <c r="B209" s="428"/>
       <c r="C209" s="36" t="s">
         <v>188</v>
       </c>
